--- a/albums/pink_floyd_discography_bot.xlsx
+++ b/albums/pink_floyd_discography_bot.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" r:id="R760f706b867c4b5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="2" r:id="R7335528a521f42ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" r:id="Rb2f857972bd74d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="2" r:id="R0c6858400db64528"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -41,7 +41,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,6 +61,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF111827"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F2937"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -114,7 +119,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -191,6 +196,27 @@
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -364,24 +390,24 @@
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="16" t="str">
+    <x:row r="1" ht="15.75" hidden="0" customHeight="1">
+      <x:c r="A1" s="30" t="str">
         <x:v>rank</x:v>
       </x:c>
-      <x:c r="B1" s="17" t="str">
+      <x:c r="B1" s="31" t="str">
         <x:v>artist</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="str">
+      <x:c r="C1" s="31" t="str">
         <x:v>album</x:v>
       </x:c>
-      <x:c r="D1" s="17" t="str">
+      <x:c r="D1" s="31" t="str">
         <x:v>genre</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A2" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -392,10 +418,10 @@
         <x:v>The Piper at the Gates of Dawn</x:v>
       </x:c>
       <x:c r="D2" s="19" t="str">
-        <x:v>psychedelic rock, psychedelic pop, space rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+        <x:v>psychedelic rock, psychedelic pop, space rock, 1967</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A3" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -406,10 +432,10 @@
         <x:v>A Saucerful of Secrets</x:v>
       </x:c>
       <x:c r="D3" s="19" t="str">
-        <x:v>psychedelic rock, space rock, experimental rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>psychedelic rock, space rock, experimental rock, 1968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A4" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -420,10 +446,10 @@
         <x:v>Soundtrack from the Film More</x:v>
       </x:c>
       <x:c r="D4" s="19" t="str">
-        <x:v>psychedelic rock, hard rock, soundtrack</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>psychedelic rock, hard rock, soundtrack, 1969</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A5" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -434,10 +460,10 @@
         <x:v>Ummagumma</x:v>
       </x:c>
       <x:c r="D5" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, experimental rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>progressive rock, psychedelic rock, experimental rock, 1969</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A6" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -448,10 +474,10 @@
         <x:v>Atom Heart Mother</x:v>
       </x:c>
       <x:c r="D6" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, symphonic rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>progressive rock, psychedelic rock, symphonic rock, 1970</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A7" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -462,10 +488,10 @@
         <x:v>Meddle</x:v>
       </x:c>
       <x:c r="D7" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, space rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>progressive rock, psychedelic rock, space rock, 1971</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A8" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -476,10 +502,10 @@
         <x:v>Obscured by Clouds</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, soundtrack</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>progressive rock, psychedelic rock, soundtrack, 1972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A9" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -490,10 +516,10 @@
         <x:v>The Dark Side of the Moon</x:v>
       </x:c>
       <x:c r="D9" s="19" t="str">
-        <x:v>progressive rock, art rock, psychedelic rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>progressive rock, art rock, psychedelic rock, 1973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A10" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -504,10 +530,10 @@
         <x:v>Wish You Were Here</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>progressive rock, art rock, space rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>progressive rock, art rock, space rock, 1975</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A11" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -518,10 +544,10 @@
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="D11" s="19" t="str">
-        <x:v>progressive rock, art rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>progressive rock, art rock, 1977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A12" s="20" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -532,10 +558,10 @@
         <x:v>The Wall</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
-        <x:v>progressive rock, art rock, rock opera</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>progressive rock, art rock, rock opera, 1979</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A13" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -546,10 +572,10 @@
         <x:v>The Final Cut</x:v>
       </x:c>
       <x:c r="D13" s="19" t="str">
-        <x:v>progressive rock, art rock, concept album</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>progressive rock, art rock, concept album, 1983</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A14" s="20" t="n">
         <x:v>13</x:v>
       </x:c>
@@ -560,10 +586,10 @@
         <x:v>A Momentary Lapse of Reason</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
-        <x:v>progressive rock, art rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>progressive rock, art rock, 1987</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A15" s="20" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -574,10 +600,10 @@
         <x:v>The Division Bell</x:v>
       </x:c>
       <x:c r="D15" s="19" t="str">
-        <x:v>progressive rock, art rock</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>progressive rock, art rock, 1994</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15.75" hidden="0" customHeight="1">
       <x:c r="A16" s="20" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -588,7 +614,7 @@
         <x:v>The Endless River</x:v>
       </x:c>
       <x:c r="D16" s="19" t="str">
-        <x:v>ambient, progressive rock, instrumental rock</x:v>
+        <x:v>ambient, progressive rock, instrumental rock, 2014</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1104,7 +1130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R581ae2f9d5d5492b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redfa91efb52a479e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1113,66 +1139,66 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="25" t="str">
-        <x:v>scope</x:v>
-      </x:c>
-      <x:c r="B1" s="25" t="str">
+      <x:c r="A1" s="32" t="str">
+        <x:v>what</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>source</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>url</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
         <x:v>note</x:v>
-      </x:c>
-      <x:c r="C1" s="25" t="str">
-        <x:v>source</x:v>
-      </x:c>
-      <x:c r="D1" s="25" t="str">
-        <x:v>url</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>main sheet</x:v>
+        <x:v>Pink Floyd studio albums list</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>Лист1 содержит полную студийную дискографию Pink Floyd: 15 studio albums, без live/compilation/box set/singles.</x:v>
+        <x:v>Pink Floyd official discography</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Wikipedia — Pink Floyd discography</x:v>
+        <x:v>https://www.pinkfloyd.com/music/albums.php</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Pink_Floyd_discography</x:v>
+        <x:v>Used to verify album list.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>main sheet</x:v>
+        <x:v>Album release years and genres</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>Официальный сайт Pink Floyd использован для сверки состава альбомов и страниц альбомов.</x:v>
+        <x:v>Wikipedia discography / album pages</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>Pink Floyd official website</x:v>
+        <x:v>https://en.wikipedia.org/wiki/Pink_Floyd_discography</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>https://www.pinkfloyd.com/</x:v>
+        <x:v>Used as a cross-check for years and genre labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>main sheet</x:v>
+        <x:v>Music metadata cross-check</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>Жанры нормализованы вручную как теги для бота, с опорой на общепринятые категории группы: psychedelic rock, space rock, progressive rock, art rock.</x:v>
+        <x:v>AllMusic Pink Floyd discography</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Wikipedia — Pink Floyd discography / official pages</x:v>
+        <x:v>https://www.allmusic.com/artist/pink-floyd-mn0000346336/discography</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Pink_Floyd_discography</x:v>
+        <x:v>Used as an additional discography cross-check.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
